--- a/data/airfoilstuff.xlsx
+++ b/data/airfoilstuff.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pansa\Desktop\SCHOOL\TU DELFT\MASTER\ROTOR WAKE\rotorwakemetboys\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EF0514A5-68D6-4F10-8054-3CCF69BE96C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B83AEEF-13E2-4BA9-9124-B00B7F9A31AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3840" yWindow="3840" windowWidth="23040" windowHeight="14100" xr2:uid="{A39D6C71-65D3-401F-9C38-F41825BADA71}"/>
+    <workbookView xWindow="2688" yWindow="2688" windowWidth="23040" windowHeight="14100" xr2:uid="{A39D6C71-65D3-401F-9C38-F41825BADA71}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -119,6 +119,1021 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-GB"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="LID4096"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$B$11</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>c/R</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="38100" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$A$12:$A$31</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.28947368000000001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.32894737000000002</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.36842105000000003</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.40789473999999998</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.44736841999999999</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.48684210999999999</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.52631578999999995</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.56578947000000002</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.60526316000000002</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.64473683999999998</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.68421052999999998</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.72368421000000005</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.76315789000000001</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.80263158000000001</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.84210525999999997</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.88157894999999997</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.92105263000000004</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.96052632000000004</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$B$12:$B$31</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>0.16500000000000001</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.16263158</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.16026315999999999</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.15789474000000001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.15552632</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.15315788999999999</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.15078947000000001</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.14842105</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.14605262999999999</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.14368421000000001</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.14131579</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.13894736999999999</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.13657895</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.13421052999999999</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.13184211000000001</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.12947368000000001</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.12710526</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.12473684</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.12236842000000001</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.12</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-5F20-4745-B75A-90B61E0763AC}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="324727231"/>
+        <c:axId val="324737311"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="324727231"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="LID4096"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="324737311"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="324737311"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="LID4096"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="324727231"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="LID4096"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>464820</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>45720</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>160020</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>45720</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3B0009FF-6253-4AEF-82F6-19ACD4400664}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -864,5 +1879,6 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/data/airfoilstuff.xlsx
+++ b/data/airfoilstuff.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pansa\Desktop\SCHOOL\TU DELFT\MASTER\ROTOR WAKE\rotorwakemetboys\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B83AEEF-13E2-4BA9-9124-B00B7F9A31AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E8EE67D-D48E-495C-B7D3-EEDD0A3F7A82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2688" yWindow="2688" windowWidth="23040" windowHeight="14100" xr2:uid="{A39D6C71-65D3-401F-9C38-F41825BADA71}"/>
+    <workbookView xWindow="5145" yWindow="-16320" windowWidth="29040" windowHeight="16440" xr2:uid="{A39D6C71-65D3-401F-9C38-F41825BADA71}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="10">
   <si>
     <t>r/R</t>
   </si>
@@ -67,6 +67,27 @@
   </si>
   <si>
     <t>beta</t>
+  </si>
+  <si>
+    <t>AoA</t>
+  </si>
+  <si>
+    <t>cl</t>
+  </si>
+  <si>
+    <t>cd</t>
+  </si>
+  <si>
+    <t>cm</t>
+  </si>
+  <si>
+    <t>---------</t>
+  </si>
+  <si>
+    <t>--------</t>
+  </si>
+  <si>
+    <t>clcd</t>
   </si>
 </sst>
 </file>
@@ -539,6 +560,731 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-GB"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="LID4096"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$W$9</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>clcd</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="38100" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:strRef>
+              <c:f>Sheet1!$S$10:$S$81</c:f>
+              <c:strCache>
+                <c:ptCount val="72"/>
+                <c:pt idx="0">
+                  <c:v>--------</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-10</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-9.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-9</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-8.5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-8</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-7.5</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-6.5</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-6</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-5.5</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-5</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-4.5</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-4</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-3.5</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>-3</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>-2.5</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>-2</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>-1.5</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>-1</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>-0.5</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>1.5</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>3.5</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>4.5</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>5.5</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>6.5</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>7.5</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>8.5</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>9.5</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>10.5</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>11.5</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>12.5</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>13.5</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>14.5</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>15.5</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>16.5</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>17.5</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>18.5</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>19.5</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>20.5</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>21.5</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>22.5</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>23.5</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>24.5</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>25</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$W$10:$W$81</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="72"/>
+                <c:pt idx="1">
+                  <c:v>-26.526838069463238</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-28.797638217928071</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-28.68452380952381</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-27.52098127824403</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-25.580912863070537</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-22.961876832844574</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-19.776061776061777</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-16.037126715092814</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-11.845637583892616</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-7.2656249999999991</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-2.3235031277926717</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2.8911253430924062</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>8.3380018674136327</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>13.937381404174573</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>19.644572526416905</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>25.397286821705428</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>31.110029211295036</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>36.770731707317076</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>42.268743914313532</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>47.633365664403492</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>52.743022136669879</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>57.645376549094379</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>62.259887005649723</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>66.610956360259991</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>70.630136986301366</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>74.283154121863802</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>77.638279192273913</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>80.626609442060087</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>83.232830820770531</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>85.542857142857144</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>87.412698412698404</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>88.936825885978436</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>90.134428678117999</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>90.939306358381501</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>91.44553072625699</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>91.555555555555543</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>91.355382619974066</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>90.816708229426453</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>89.970077797725921</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>88.795871559633028</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>87.280701754385973</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>85.507853403141368</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>83.41317365269461</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>80.953962980541064</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>78.007213706041483</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>74.477928692699479</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>70.691848906560637</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>66.593854128100702</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>62.240493319630005</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>57.694488188976379</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>52.983615981603904</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>48.2109375</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>43.42308592835402</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>38.719448506371421</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>34.143094841930115</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>29.753486863444696</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>25.612475303415181</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>21.756394640682093</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>18.213875847678665</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>14.991580253478684</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>12.186632660715624</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>9.9493719559087399</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>8.4385232019871292</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>7.4615699938511986</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>6.8004369300911849</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>6.2534886811677675</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>5.8632385578493356</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>5.5453350854139289</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>5.2824805021875605</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>5.0633281016169658</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>4.8803037227124131</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-D712-44F2-9864-D9674DF10896}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="205772927"/>
+        <c:axId val="205773407"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="205772927"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="LID4096"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="205773407"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="205773407"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="LID4096"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="205772927"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="LID4096"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -579,7 +1325,563 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -1128,6 +2430,42 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>102213</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>74951</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>408326</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>74951</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F80801A9-EFA7-4076-2782-6BF96E154458}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1453,10 +2791,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4E4ED6B-38DF-447A-B27F-4A070C7129BB}">
-  <dimension ref="A2:T31"/>
+  <dimension ref="A2:W81"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>0.25</v>
       </c>
@@ -1518,7 +2856,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>0.16500000000000001</v>
       </c>
@@ -1580,7 +2918,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>68.5</v>
       </c>
@@ -1642,7 +2980,35 @@
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="S9" t="s">
+        <v>3</v>
+      </c>
+      <c r="T9" t="s">
+        <v>4</v>
+      </c>
+      <c r="U9" t="s">
+        <v>5</v>
+      </c>
+      <c r="V9" t="s">
+        <v>6</v>
+      </c>
+      <c r="W9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="S10" t="s">
+        <v>8</v>
+      </c>
+      <c r="T10" t="s">
+        <v>7</v>
+      </c>
+      <c r="U10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>0</v>
       </c>
@@ -1652,8 +3018,24 @@
       <c r="C11" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="S11">
+        <v>-10</v>
+      </c>
+      <c r="T11">
+        <v>-0.58809999999999996</v>
+      </c>
+      <c r="U11">
+        <v>2.2169999999999999E-2</v>
+      </c>
+      <c r="V11">
+        <v>-0.10539999999999999</v>
+      </c>
+      <c r="W11">
+        <f>T11/U11</f>
+        <v>-26.526838069463238</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A12" cm="1">
         <f t="array" ref="A12:A31">TRANSPOSE(A2:T2)</f>
         <v>0.25</v>
@@ -1666,8 +3048,24 @@
         <f t="array" ref="C12:C31">TRANSPOSE(A5:T5)</f>
         <v>68.5</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="S12">
+        <v>-9.5</v>
+      </c>
+      <c r="T12">
+        <v>-0.53649999999999998</v>
+      </c>
+      <c r="U12">
+        <v>1.8630000000000001E-2</v>
+      </c>
+      <c r="V12">
+        <v>-0.1069</v>
+      </c>
+      <c r="W12">
+        <f t="shared" ref="W12:W75" si="0">T12/U12</f>
+        <v>-28.797638217928071</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>0.28947368000000001</v>
       </c>
@@ -1677,8 +3075,24 @@
       <c r="C13">
         <v>66.526315789999998</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="S13">
+        <v>-9</v>
+      </c>
+      <c r="T13">
+        <v>-0.4819</v>
+      </c>
+      <c r="U13">
+        <v>1.6799999999999999E-2</v>
+      </c>
+      <c r="V13">
+        <v>-0.1076</v>
+      </c>
+      <c r="W13">
+        <f t="shared" si="0"/>
+        <v>-28.68452380952381</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>0.32894737000000002</v>
       </c>
@@ -1688,8 +3102,24 @@
       <c r="C14">
         <v>64.552631579999996</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="S14">
+        <v>-8.5</v>
+      </c>
+      <c r="T14">
+        <v>-0.42630000000000001</v>
+      </c>
+      <c r="U14">
+        <v>1.549E-2</v>
+      </c>
+      <c r="V14">
+        <v>-0.1082</v>
+      </c>
+      <c r="W14">
+        <f t="shared" si="0"/>
+        <v>-27.52098127824403</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>0.36842105000000003</v>
       </c>
@@ -1699,8 +3129,24 @@
       <c r="C15">
         <v>62.578947370000002</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="S15">
+        <v>-8</v>
+      </c>
+      <c r="T15">
+        <v>-0.36990000000000001</v>
+      </c>
+      <c r="U15">
+        <v>1.4460000000000001E-2</v>
+      </c>
+      <c r="V15">
+        <v>-0.1086</v>
+      </c>
+      <c r="W15">
+        <f t="shared" si="0"/>
+        <v>-25.580912863070537</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>0.40789473999999998</v>
       </c>
@@ -1710,8 +3156,24 @@
       <c r="C16">
         <v>60.60526316</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="S16">
+        <v>-7.5</v>
+      </c>
+      <c r="T16">
+        <v>-0.31319999999999998</v>
+      </c>
+      <c r="U16">
+        <v>1.3639999999999999E-2</v>
+      </c>
+      <c r="V16">
+        <v>-0.1089</v>
+      </c>
+      <c r="W16">
+        <f t="shared" si="0"/>
+        <v>-22.961876832844574</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>0.44736841999999999</v>
       </c>
@@ -1721,8 +3183,24 @@
       <c r="C17">
         <v>58.631578949999998</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="S17">
+        <v>-7</v>
+      </c>
+      <c r="T17">
+        <v>-0.25609999999999999</v>
+      </c>
+      <c r="U17">
+        <v>1.295E-2</v>
+      </c>
+      <c r="V17">
+        <v>-0.10920000000000001</v>
+      </c>
+      <c r="W17">
+        <f t="shared" si="0"/>
+        <v>-19.776061776061777</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>0.48684210999999999</v>
       </c>
@@ -1732,8 +3210,24 @@
       <c r="C18">
         <v>56.657894740000003</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="S18">
+        <v>-6.5</v>
+      </c>
+      <c r="T18">
+        <v>-0.19869999999999999</v>
+      </c>
+      <c r="U18">
+        <v>1.239E-2</v>
+      </c>
+      <c r="V18">
+        <v>-0.1095</v>
+      </c>
+      <c r="W18">
+        <f t="shared" si="0"/>
+        <v>-16.037126715092814</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>0.52631578999999995</v>
       </c>
@@ -1743,8 +3237,24 @@
       <c r="C19">
         <v>54.684210530000001</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="S19">
+        <v>-6</v>
+      </c>
+      <c r="T19">
+        <v>-0.14119999999999999</v>
+      </c>
+      <c r="U19">
+        <v>1.192E-2</v>
+      </c>
+      <c r="V19">
+        <v>-0.10970000000000001</v>
+      </c>
+      <c r="W19">
+        <f t="shared" si="0"/>
+        <v>-11.845637583892616</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>0.56578947000000002</v>
       </c>
@@ -1754,8 +3264,24 @@
       <c r="C20">
         <v>52.71052632</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="S20">
+        <v>-5.5</v>
+      </c>
+      <c r="T20">
+        <v>-8.3699999999999997E-2</v>
+      </c>
+      <c r="U20">
+        <v>1.1520000000000001E-2</v>
+      </c>
+      <c r="V20">
+        <v>-0.11</v>
+      </c>
+      <c r="W20">
+        <f t="shared" si="0"/>
+        <v>-7.2656249999999991</v>
+      </c>
+    </row>
+    <row r="21" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>0.60526316000000002</v>
       </c>
@@ -1765,8 +3291,24 @@
       <c r="C21">
         <v>50.736842109999998</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="S21">
+        <v>-5</v>
+      </c>
+      <c r="T21">
+        <v>-2.5999999999999999E-2</v>
+      </c>
+      <c r="U21">
+        <v>1.119E-2</v>
+      </c>
+      <c r="V21">
+        <v>-0.11020000000000001</v>
+      </c>
+      <c r="W21">
+        <f t="shared" si="0"/>
+        <v>-2.3235031277926717</v>
+      </c>
+    </row>
+    <row r="22" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>0.64473683999999998</v>
       </c>
@@ -1776,8 +3318,24 @@
       <c r="C22">
         <v>48.763157890000002</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="S22">
+        <v>-4.5</v>
+      </c>
+      <c r="T22">
+        <v>3.1600000000000003E-2</v>
+      </c>
+      <c r="U22">
+        <v>1.093E-2</v>
+      </c>
+      <c r="V22">
+        <v>-0.1104</v>
+      </c>
+      <c r="W22">
+        <f t="shared" si="0"/>
+        <v>2.8911253430924062</v>
+      </c>
+    </row>
+    <row r="23" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>0.68421052999999998</v>
       </c>
@@ -1787,8 +3345,24 @@
       <c r="C23">
         <v>46.78947368</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="S23">
+        <v>-4</v>
+      </c>
+      <c r="T23">
+        <v>8.9300000000000004E-2</v>
+      </c>
+      <c r="U23">
+        <v>1.0710000000000001E-2</v>
+      </c>
+      <c r="V23">
+        <v>-0.1105</v>
+      </c>
+      <c r="W23">
+        <f t="shared" si="0"/>
+        <v>8.3380018674136327</v>
+      </c>
+    </row>
+    <row r="24" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>0.72368421000000005</v>
       </c>
@@ -1798,8 +3372,24 @@
       <c r="C24">
         <v>44.815789469999999</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="S24">
+        <v>-3.5</v>
+      </c>
+      <c r="T24">
+        <v>0.1469</v>
+      </c>
+      <c r="U24">
+        <v>1.0540000000000001E-2</v>
+      </c>
+      <c r="V24">
+        <v>-0.11070000000000001</v>
+      </c>
+      <c r="W24">
+        <f t="shared" si="0"/>
+        <v>13.937381404174573</v>
+      </c>
+    </row>
+    <row r="25" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>0.76315789000000001</v>
       </c>
@@ -1809,8 +3399,24 @@
       <c r="C25">
         <v>42.842105259999997</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="S25">
+        <v>-3</v>
+      </c>
+      <c r="T25">
+        <v>0.20449999999999999</v>
+      </c>
+      <c r="U25">
+        <v>1.0410000000000001E-2</v>
+      </c>
+      <c r="V25">
+        <v>-0.1109</v>
+      </c>
+      <c r="W25">
+        <f t="shared" si="0"/>
+        <v>19.644572526416905</v>
+      </c>
+    </row>
+    <row r="26" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>0.80263158000000001</v>
       </c>
@@ -1820,8 +3426,24 @@
       <c r="C26">
         <v>40.868421050000002</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="S26">
+        <v>-2.5</v>
+      </c>
+      <c r="T26">
+        <v>0.2621</v>
+      </c>
+      <c r="U26">
+        <v>1.0319999999999999E-2</v>
+      </c>
+      <c r="V26">
+        <v>-0.111</v>
+      </c>
+      <c r="W26">
+        <f t="shared" si="0"/>
+        <v>25.397286821705428</v>
+      </c>
+    </row>
+    <row r="27" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>0.84210525999999997</v>
       </c>
@@ -1831,8 +3453,24 @@
       <c r="C27">
         <v>38.89473684</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="S27">
+        <v>-2</v>
+      </c>
+      <c r="T27">
+        <v>0.31950000000000001</v>
+      </c>
+      <c r="U27">
+        <v>1.027E-2</v>
+      </c>
+      <c r="V27">
+        <v>-0.1111</v>
+      </c>
+      <c r="W27">
+        <f t="shared" si="0"/>
+        <v>31.110029211295036</v>
+      </c>
+    </row>
+    <row r="28" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>0.88157894999999997</v>
       </c>
@@ -1842,8 +3480,24 @@
       <c r="C28">
         <v>36.921052629999998</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="S28">
+        <v>-1.5</v>
+      </c>
+      <c r="T28">
+        <v>0.37690000000000001</v>
+      </c>
+      <c r="U28">
+        <v>1.025E-2</v>
+      </c>
+      <c r="V28">
+        <v>-0.11119999999999999</v>
+      </c>
+      <c r="W28">
+        <f t="shared" si="0"/>
+        <v>36.770731707317076</v>
+      </c>
+    </row>
+    <row r="29" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>0.92105263000000004</v>
       </c>
@@ -1853,8 +3507,24 @@
       <c r="C29">
         <v>34.947368419999997</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="S29">
+        <v>-1</v>
+      </c>
+      <c r="T29">
+        <v>0.43409999999999999</v>
+      </c>
+      <c r="U29">
+        <v>1.027E-2</v>
+      </c>
+      <c r="V29">
+        <v>-0.1114</v>
+      </c>
+      <c r="W29">
+        <f t="shared" si="0"/>
+        <v>42.268743914313532</v>
+      </c>
+    </row>
+    <row r="30" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>0.96052632000000004</v>
       </c>
@@ -1864,8 +3534,24 @@
       <c r="C30">
         <v>32.973684210000002</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="S30">
+        <v>-0.5</v>
+      </c>
+      <c r="T30">
+        <v>0.49109999999999998</v>
+      </c>
+      <c r="U30">
+        <v>1.031E-2</v>
+      </c>
+      <c r="V30">
+        <v>-0.1114</v>
+      </c>
+      <c r="W30">
+        <f t="shared" si="0"/>
+        <v>47.633365664403492</v>
+      </c>
+    </row>
+    <row r="31" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>1</v>
       </c>
@@ -1874,6 +3560,922 @@
       </c>
       <c r="C31">
         <v>31</v>
+      </c>
+      <c r="S31">
+        <v>0</v>
+      </c>
+      <c r="T31">
+        <v>0.54800000000000004</v>
+      </c>
+      <c r="U31">
+        <v>1.039E-2</v>
+      </c>
+      <c r="V31">
+        <v>-0.1115</v>
+      </c>
+      <c r="W31">
+        <f t="shared" si="0"/>
+        <v>52.743022136669879</v>
+      </c>
+    </row>
+    <row r="32" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="S32">
+        <v>0.5</v>
+      </c>
+      <c r="T32">
+        <v>0.60470000000000002</v>
+      </c>
+      <c r="U32">
+        <v>1.0489999999999999E-2</v>
+      </c>
+      <c r="V32">
+        <v>-0.1116</v>
+      </c>
+      <c r="W32">
+        <f t="shared" si="0"/>
+        <v>57.645376549094379</v>
+      </c>
+    </row>
+    <row r="33" spans="19:23" x14ac:dyDescent="0.3">
+      <c r="S33">
+        <v>1</v>
+      </c>
+      <c r="T33">
+        <v>0.66120000000000001</v>
+      </c>
+      <c r="U33">
+        <v>1.0619999999999999E-2</v>
+      </c>
+      <c r="V33">
+        <v>-0.1116</v>
+      </c>
+      <c r="W33">
+        <f t="shared" si="0"/>
+        <v>62.259887005649723</v>
+      </c>
+    </row>
+    <row r="34" spans="19:23" x14ac:dyDescent="0.3">
+      <c r="S34">
+        <v>1.5</v>
+      </c>
+      <c r="T34">
+        <v>0.71740000000000004</v>
+      </c>
+      <c r="U34">
+        <v>1.077E-2</v>
+      </c>
+      <c r="V34">
+        <v>-0.1116</v>
+      </c>
+      <c r="W34">
+        <f t="shared" si="0"/>
+        <v>66.610956360259991</v>
+      </c>
+    </row>
+    <row r="35" spans="19:23" x14ac:dyDescent="0.3">
+      <c r="S35">
+        <v>2</v>
+      </c>
+      <c r="T35">
+        <v>0.77339999999999998</v>
+      </c>
+      <c r="U35">
+        <v>1.095E-2</v>
+      </c>
+      <c r="V35">
+        <v>-0.1116</v>
+      </c>
+      <c r="W35">
+        <f t="shared" si="0"/>
+        <v>70.630136986301366</v>
+      </c>
+    </row>
+    <row r="36" spans="19:23" x14ac:dyDescent="0.3">
+      <c r="S36">
+        <v>2.5</v>
+      </c>
+      <c r="T36">
+        <v>0.82899999999999996</v>
+      </c>
+      <c r="U36">
+        <v>1.116E-2</v>
+      </c>
+      <c r="V36">
+        <v>-0.1115</v>
+      </c>
+      <c r="W36">
+        <f t="shared" si="0"/>
+        <v>74.283154121863802</v>
+      </c>
+    </row>
+    <row r="37" spans="19:23" x14ac:dyDescent="0.3">
+      <c r="S37">
+        <v>3</v>
+      </c>
+      <c r="T37">
+        <v>0.88429999999999997</v>
+      </c>
+      <c r="U37">
+        <v>1.1390000000000001E-2</v>
+      </c>
+      <c r="V37">
+        <v>-0.1114</v>
+      </c>
+      <c r="W37">
+        <f t="shared" si="0"/>
+        <v>77.638279192273913</v>
+      </c>
+    </row>
+    <row r="38" spans="19:23" x14ac:dyDescent="0.3">
+      <c r="S38">
+        <v>3.5</v>
+      </c>
+      <c r="T38">
+        <v>0.93930000000000002</v>
+      </c>
+      <c r="U38">
+        <v>1.1650000000000001E-2</v>
+      </c>
+      <c r="V38">
+        <v>-0.11119999999999999</v>
+      </c>
+      <c r="W38">
+        <f t="shared" si="0"/>
+        <v>80.626609442060087</v>
+      </c>
+    </row>
+    <row r="39" spans="19:23" x14ac:dyDescent="0.3">
+      <c r="S39">
+        <v>4</v>
+      </c>
+      <c r="T39">
+        <v>0.99380000000000002</v>
+      </c>
+      <c r="U39">
+        <v>1.1939999999999999E-2</v>
+      </c>
+      <c r="V39">
+        <v>-0.111</v>
+      </c>
+      <c r="W39">
+        <f t="shared" si="0"/>
+        <v>83.232830820770531</v>
+      </c>
+    </row>
+    <row r="40" spans="19:23" x14ac:dyDescent="0.3">
+      <c r="S40">
+        <v>4.5</v>
+      </c>
+      <c r="T40">
+        <v>1.0479000000000001</v>
+      </c>
+      <c r="U40">
+        <v>1.225E-2</v>
+      </c>
+      <c r="V40">
+        <v>-0.1108</v>
+      </c>
+      <c r="W40">
+        <f t="shared" si="0"/>
+        <v>85.542857142857144</v>
+      </c>
+    </row>
+    <row r="41" spans="19:23" x14ac:dyDescent="0.3">
+      <c r="S41">
+        <v>5</v>
+      </c>
+      <c r="T41">
+        <v>1.1013999999999999</v>
+      </c>
+      <c r="U41">
+        <v>1.26E-2</v>
+      </c>
+      <c r="V41">
+        <v>-0.1104</v>
+      </c>
+      <c r="W41">
+        <f t="shared" si="0"/>
+        <v>87.412698412698404</v>
+      </c>
+    </row>
+    <row r="42" spans="19:23" x14ac:dyDescent="0.3">
+      <c r="S42">
+        <v>5.5</v>
+      </c>
+      <c r="T42">
+        <v>1.1544000000000001</v>
+      </c>
+      <c r="U42">
+        <v>1.298E-2</v>
+      </c>
+      <c r="V42">
+        <v>-0.11</v>
+      </c>
+      <c r="W42">
+        <f t="shared" si="0"/>
+        <v>88.936825885978436</v>
+      </c>
+    </row>
+    <row r="43" spans="19:23" x14ac:dyDescent="0.3">
+      <c r="S43">
+        <v>6</v>
+      </c>
+      <c r="T43">
+        <v>1.2069000000000001</v>
+      </c>
+      <c r="U43">
+        <v>1.3390000000000001E-2</v>
+      </c>
+      <c r="V43">
+        <v>-0.1095</v>
+      </c>
+      <c r="W43">
+        <f t="shared" si="0"/>
+        <v>90.134428678117999</v>
+      </c>
+    </row>
+    <row r="44" spans="19:23" x14ac:dyDescent="0.3">
+      <c r="S44">
+        <v>6.5</v>
+      </c>
+      <c r="T44">
+        <v>1.2585999999999999</v>
+      </c>
+      <c r="U44">
+        <v>1.384E-2</v>
+      </c>
+      <c r="V44">
+        <v>-0.109</v>
+      </c>
+      <c r="W44">
+        <f t="shared" si="0"/>
+        <v>90.939306358381501</v>
+      </c>
+    </row>
+    <row r="45" spans="19:23" x14ac:dyDescent="0.3">
+      <c r="S45">
+        <v>7</v>
+      </c>
+      <c r="T45">
+        <v>1.3095000000000001</v>
+      </c>
+      <c r="U45">
+        <v>1.4319999999999999E-2</v>
+      </c>
+      <c r="V45">
+        <v>-0.10829999999999999</v>
+      </c>
+      <c r="W45">
+        <f t="shared" si="0"/>
+        <v>91.44553072625699</v>
+      </c>
+    </row>
+    <row r="46" spans="19:23" x14ac:dyDescent="0.3">
+      <c r="S46">
+        <v>7.5</v>
+      </c>
+      <c r="T46">
+        <v>1.3595999999999999</v>
+      </c>
+      <c r="U46">
+        <v>1.485E-2</v>
+      </c>
+      <c r="V46">
+        <v>-0.1075</v>
+      </c>
+      <c r="W46">
+        <f t="shared" si="0"/>
+        <v>91.555555555555543</v>
+      </c>
+    </row>
+    <row r="47" spans="19:23" x14ac:dyDescent="0.3">
+      <c r="S47">
+        <v>8</v>
+      </c>
+      <c r="T47">
+        <v>1.4087000000000001</v>
+      </c>
+      <c r="U47">
+        <v>1.542E-2</v>
+      </c>
+      <c r="V47">
+        <v>-0.1065</v>
+      </c>
+      <c r="W47">
+        <f t="shared" si="0"/>
+        <v>91.355382619974066</v>
+      </c>
+    </row>
+    <row r="48" spans="19:23" x14ac:dyDescent="0.3">
+      <c r="S48">
+        <v>8.5</v>
+      </c>
+      <c r="T48">
+        <v>1.4567000000000001</v>
+      </c>
+      <c r="U48">
+        <v>1.6039999999999999E-2</v>
+      </c>
+      <c r="V48">
+        <v>-0.10539999999999999</v>
+      </c>
+      <c r="W48">
+        <f t="shared" si="0"/>
+        <v>90.816708229426453</v>
+      </c>
+    </row>
+    <row r="49" spans="19:23" x14ac:dyDescent="0.3">
+      <c r="S49">
+        <v>9</v>
+      </c>
+      <c r="T49">
+        <v>1.5034000000000001</v>
+      </c>
+      <c r="U49">
+        <v>1.6709999999999999E-2</v>
+      </c>
+      <c r="V49">
+        <v>-0.1041</v>
+      </c>
+      <c r="W49">
+        <f t="shared" si="0"/>
+        <v>89.970077797725921</v>
+      </c>
+    </row>
+    <row r="50" spans="19:23" x14ac:dyDescent="0.3">
+      <c r="S50">
+        <v>9.5</v>
+      </c>
+      <c r="T50">
+        <v>1.5486</v>
+      </c>
+      <c r="U50">
+        <v>1.7440000000000001E-2</v>
+      </c>
+      <c r="V50">
+        <v>-0.1026</v>
+      </c>
+      <c r="W50">
+        <f t="shared" si="0"/>
+        <v>88.795871559633028</v>
+      </c>
+    </row>
+    <row r="51" spans="19:23" x14ac:dyDescent="0.3">
+      <c r="S51">
+        <v>10</v>
+      </c>
+      <c r="T51">
+        <v>1.5920000000000001</v>
+      </c>
+      <c r="U51">
+        <v>1.8239999999999999E-2</v>
+      </c>
+      <c r="V51">
+        <v>-0.1008</v>
+      </c>
+      <c r="W51">
+        <f t="shared" si="0"/>
+        <v>87.280701754385973</v>
+      </c>
+    </row>
+    <row r="52" spans="19:23" x14ac:dyDescent="0.3">
+      <c r="S52">
+        <v>10.5</v>
+      </c>
+      <c r="T52">
+        <v>1.6332</v>
+      </c>
+      <c r="U52">
+        <v>1.9099999999999999E-2</v>
+      </c>
+      <c r="V52">
+        <v>-9.8599999999999993E-2</v>
+      </c>
+      <c r="W52">
+        <f t="shared" si="0"/>
+        <v>85.507853403141368</v>
+      </c>
+    </row>
+    <row r="53" spans="19:23" x14ac:dyDescent="0.3">
+      <c r="S53">
+        <v>11</v>
+      </c>
+      <c r="T53">
+        <v>1.6716</v>
+      </c>
+      <c r="U53">
+        <v>2.0039999999999999E-2</v>
+      </c>
+      <c r="V53">
+        <v>-9.6100000000000005E-2</v>
+      </c>
+      <c r="W53">
+        <f t="shared" si="0"/>
+        <v>83.41317365269461</v>
+      </c>
+    </row>
+    <row r="54" spans="19:23" x14ac:dyDescent="0.3">
+      <c r="S54">
+        <v>11.5</v>
+      </c>
+      <c r="T54">
+        <v>1.7057</v>
+      </c>
+      <c r="U54">
+        <v>2.1069999999999998E-2</v>
+      </c>
+      <c r="V54">
+        <v>-9.2799999999999994E-2</v>
+      </c>
+      <c r="W54">
+        <f t="shared" si="0"/>
+        <v>80.953962980541064</v>
+      </c>
+    </row>
+    <row r="55" spans="19:23" x14ac:dyDescent="0.3">
+      <c r="S55">
+        <v>12</v>
+      </c>
+      <c r="T55">
+        <v>1.7302</v>
+      </c>
+      <c r="U55">
+        <v>2.2179999999999998E-2</v>
+      </c>
+      <c r="V55">
+        <v>-8.77E-2</v>
+      </c>
+      <c r="W55">
+        <f t="shared" si="0"/>
+        <v>78.007213706041483</v>
+      </c>
+    </row>
+    <row r="56" spans="19:23" x14ac:dyDescent="0.3">
+      <c r="S56">
+        <v>12.5</v>
+      </c>
+      <c r="T56">
+        <v>1.7546999999999999</v>
+      </c>
+      <c r="U56">
+        <v>2.3560000000000001E-2</v>
+      </c>
+      <c r="V56">
+        <v>-8.3099999999999993E-2</v>
+      </c>
+      <c r="W56">
+        <f t="shared" si="0"/>
+        <v>74.477928692699479</v>
+      </c>
+    </row>
+    <row r="57" spans="19:23" x14ac:dyDescent="0.3">
+      <c r="S57">
+        <v>13</v>
+      </c>
+      <c r="T57">
+        <v>1.7779</v>
+      </c>
+      <c r="U57">
+        <v>2.5149999999999999E-2</v>
+      </c>
+      <c r="V57">
+        <v>-7.8799999999999995E-2</v>
+      </c>
+      <c r="W57">
+        <f t="shared" si="0"/>
+        <v>70.691848906560637</v>
+      </c>
+    </row>
+    <row r="58" spans="19:23" x14ac:dyDescent="0.3">
+      <c r="S58">
+        <v>13.5</v>
+      </c>
+      <c r="T58">
+        <v>1.7987</v>
+      </c>
+      <c r="U58">
+        <v>2.7009999999999999E-2</v>
+      </c>
+      <c r="V58">
+        <v>-7.4700000000000003E-2</v>
+      </c>
+      <c r="W58">
+        <f t="shared" si="0"/>
+        <v>66.593854128100702</v>
+      </c>
+    </row>
+    <row r="59" spans="19:23" x14ac:dyDescent="0.3">
+      <c r="S59">
+        <v>14</v>
+      </c>
+      <c r="T59">
+        <v>1.8168</v>
+      </c>
+      <c r="U59">
+        <v>2.9190000000000001E-2</v>
+      </c>
+      <c r="V59">
+        <v>-7.0599999999999996E-2</v>
+      </c>
+      <c r="W59">
+        <f t="shared" si="0"/>
+        <v>62.240493319630005</v>
+      </c>
+    </row>
+    <row r="60" spans="19:23" x14ac:dyDescent="0.3">
+      <c r="S60">
+        <v>14.5</v>
+      </c>
+      <c r="T60">
+        <v>1.8318000000000001</v>
+      </c>
+      <c r="U60">
+        <v>3.175E-2</v>
+      </c>
+      <c r="V60">
+        <v>-6.6799999999999998E-2</v>
+      </c>
+      <c r="W60">
+        <f t="shared" si="0"/>
+        <v>57.694488188976379</v>
+      </c>
+    </row>
+    <row r="61" spans="19:23" x14ac:dyDescent="0.3">
+      <c r="S61">
+        <v>15</v>
+      </c>
+      <c r="T61">
+        <v>1.8432999999999999</v>
+      </c>
+      <c r="U61">
+        <v>3.4790000000000001E-2</v>
+      </c>
+      <c r="V61">
+        <v>-6.3299999999999995E-2</v>
+      </c>
+      <c r="W61">
+        <f t="shared" si="0"/>
+        <v>52.983615981603904</v>
+      </c>
+    </row>
+    <row r="62" spans="19:23" x14ac:dyDescent="0.3">
+      <c r="S62">
+        <v>15.5</v>
+      </c>
+      <c r="T62">
+        <v>1.8512999999999999</v>
+      </c>
+      <c r="U62">
+        <v>3.8399999999999997E-2</v>
+      </c>
+      <c r="V62">
+        <v>-6.0199999999999997E-2</v>
+      </c>
+      <c r="W62">
+        <f t="shared" si="0"/>
+        <v>48.2109375</v>
+      </c>
+    </row>
+    <row r="63" spans="19:23" x14ac:dyDescent="0.3">
+      <c r="S63">
+        <v>16</v>
+      </c>
+      <c r="T63">
+        <v>1.8546</v>
+      </c>
+      <c r="U63">
+        <v>4.2709999999999998E-2</v>
+      </c>
+      <c r="V63">
+        <v>-5.7599999999999998E-2</v>
+      </c>
+      <c r="W63">
+        <f t="shared" si="0"/>
+        <v>43.42308592835402</v>
+      </c>
+    </row>
+    <row r="64" spans="19:23" x14ac:dyDescent="0.3">
+      <c r="S64">
+        <v>16.5</v>
+      </c>
+      <c r="T64">
+        <v>1.8534999999999999</v>
+      </c>
+      <c r="U64">
+        <v>4.7870000000000003E-2</v>
+      </c>
+      <c r="V64">
+        <v>-5.5599999999999997E-2</v>
+      </c>
+      <c r="W64">
+        <f t="shared" si="0"/>
+        <v>38.719448506371421</v>
+      </c>
+    </row>
+    <row r="65" spans="19:23" x14ac:dyDescent="0.3">
+      <c r="S65">
+        <v>17</v>
+      </c>
+      <c r="T65">
+        <v>1.8468</v>
+      </c>
+      <c r="U65">
+        <v>5.4089999999999999E-2</v>
+      </c>
+      <c r="V65">
+        <v>-5.4600000000000003E-2</v>
+      </c>
+      <c r="W65">
+        <f t="shared" si="0"/>
+        <v>34.143094841930115</v>
+      </c>
+    </row>
+    <row r="66" spans="19:23" x14ac:dyDescent="0.3">
+      <c r="S66">
+        <v>17.5</v>
+      </c>
+      <c r="T66">
+        <v>1.8346</v>
+      </c>
+      <c r="U66">
+        <v>6.166E-2</v>
+      </c>
+      <c r="V66">
+        <v>-5.4699999999999999E-2</v>
+      </c>
+      <c r="W66">
+        <f t="shared" si="0"/>
+        <v>29.753486863444696</v>
+      </c>
+    </row>
+    <row r="67" spans="19:23" x14ac:dyDescent="0.3">
+      <c r="S67">
+        <v>18</v>
+      </c>
+      <c r="T67">
+        <v>1.8149</v>
+      </c>
+      <c r="U67">
+        <v>7.0860000000000006E-2</v>
+      </c>
+      <c r="V67">
+        <v>-5.6099999999999997E-2</v>
+      </c>
+      <c r="W67">
+        <f t="shared" si="0"/>
+        <v>25.612475303415181</v>
+      </c>
+    </row>
+    <row r="68" spans="19:23" x14ac:dyDescent="0.3">
+      <c r="S68">
+        <v>18.5</v>
+      </c>
+      <c r="T68">
+        <v>1.7862</v>
+      </c>
+      <c r="U68">
+        <v>8.2100000000000006E-2</v>
+      </c>
+      <c r="V68">
+        <v>-5.8999999999999997E-2</v>
+      </c>
+      <c r="W68">
+        <f t="shared" si="0"/>
+        <v>21.756394640682093</v>
+      </c>
+    </row>
+    <row r="69" spans="19:23" x14ac:dyDescent="0.3">
+      <c r="S69">
+        <v>19</v>
+      </c>
+      <c r="T69">
+        <v>1.7458</v>
+      </c>
+      <c r="U69">
+        <v>9.5850000000000005E-2</v>
+      </c>
+      <c r="V69">
+        <v>-6.3600000000000004E-2</v>
+      </c>
+      <c r="W69">
+        <f t="shared" si="0"/>
+        <v>18.213875847678665</v>
+      </c>
+    </row>
+    <row r="70" spans="19:23" x14ac:dyDescent="0.3">
+      <c r="S70">
+        <v>19.5</v>
+      </c>
+      <c r="T70">
+        <v>1.6915</v>
+      </c>
+      <c r="U70">
+        <v>0.11283</v>
+      </c>
+      <c r="V70">
+        <v>-7.0599999999999996E-2</v>
+      </c>
+      <c r="W70">
+        <f t="shared" si="0"/>
+        <v>14.991580253478684</v>
+      </c>
+    </row>
+    <row r="71" spans="19:23" x14ac:dyDescent="0.3">
+      <c r="S71">
+        <v>20</v>
+      </c>
+      <c r="T71">
+        <v>1.6246</v>
+      </c>
+      <c r="U71">
+        <v>0.13331000000000001</v>
+      </c>
+      <c r="V71">
+        <v>-8.0399999999999999E-2</v>
+      </c>
+      <c r="W71">
+        <f t="shared" si="0"/>
+        <v>12.186632660715624</v>
+      </c>
+    </row>
+    <row r="72" spans="19:23" x14ac:dyDescent="0.3">
+      <c r="S72">
+        <v>20.5</v>
+      </c>
+      <c r="T72">
+        <v>1.5525</v>
+      </c>
+      <c r="U72">
+        <v>0.15604000000000001</v>
+      </c>
+      <c r="V72">
+        <v>-9.2799999999999994E-2</v>
+      </c>
+      <c r="W72">
+        <f t="shared" si="0"/>
+        <v>9.9493719559087399</v>
+      </c>
+    </row>
+    <row r="73" spans="19:23" x14ac:dyDescent="0.3">
+      <c r="S73">
+        <v>21</v>
+      </c>
+      <c r="T73">
+        <v>1.4947999999999999</v>
+      </c>
+      <c r="U73">
+        <v>0.17713999999999999</v>
+      </c>
+      <c r="V73">
+        <v>-0.106</v>
+      </c>
+      <c r="W73">
+        <f t="shared" si="0"/>
+        <v>8.4385232019871292</v>
+      </c>
+    </row>
+    <row r="74" spans="19:23" x14ac:dyDescent="0.3">
+      <c r="S74">
+        <v>21.5</v>
+      </c>
+      <c r="T74">
+        <v>1.4561999999999999</v>
+      </c>
+      <c r="U74">
+        <v>0.19516</v>
+      </c>
+      <c r="V74">
+        <v>-0.11799999999999999</v>
+      </c>
+      <c r="W74">
+        <f t="shared" si="0"/>
+        <v>7.4615699938511986</v>
+      </c>
+    </row>
+    <row r="75" spans="19:23" x14ac:dyDescent="0.3">
+      <c r="S75">
+        <v>22</v>
+      </c>
+      <c r="T75">
+        <v>1.4319</v>
+      </c>
+      <c r="U75">
+        <v>0.21056</v>
+      </c>
+      <c r="V75">
+        <v>-0.12870000000000001</v>
+      </c>
+      <c r="W75">
+        <f t="shared" si="0"/>
+        <v>6.8004369300911849</v>
+      </c>
+    </row>
+    <row r="76" spans="19:23" x14ac:dyDescent="0.3">
+      <c r="S76">
+        <v>22.5</v>
+      </c>
+      <c r="T76">
+        <v>1.4116</v>
+      </c>
+      <c r="U76">
+        <v>0.22572999999999999</v>
+      </c>
+      <c r="V76">
+        <v>-0.13969999999999999</v>
+      </c>
+      <c r="W76">
+        <f t="shared" ref="W76:W81" si="1">T76/U76</f>
+        <v>6.2534886811677675</v>
+      </c>
+    </row>
+    <row r="77" spans="19:23" x14ac:dyDescent="0.3">
+      <c r="S77">
+        <v>23</v>
+      </c>
+      <c r="T77">
+        <v>1.4001999999999999</v>
+      </c>
+      <c r="U77">
+        <v>0.23880999999999999</v>
+      </c>
+      <c r="V77">
+        <v>-0.14940000000000001</v>
+      </c>
+      <c r="W77">
+        <f t="shared" si="1"/>
+        <v>5.8632385578493356</v>
+      </c>
+    </row>
+    <row r="78" spans="19:23" x14ac:dyDescent="0.3">
+      <c r="S78">
+        <v>23.5</v>
+      </c>
+      <c r="T78">
+        <v>1.3926000000000001</v>
+      </c>
+      <c r="U78">
+        <v>0.25113000000000002</v>
+      </c>
+      <c r="V78">
+        <v>-0.15870000000000001</v>
+      </c>
+      <c r="W78">
+        <f t="shared" si="1"/>
+        <v>5.5453350854139289</v>
+      </c>
+    </row>
+    <row r="79" spans="19:23" x14ac:dyDescent="0.3">
+      <c r="S79">
+        <v>24</v>
+      </c>
+      <c r="T79">
+        <v>1.3885000000000001</v>
+      </c>
+      <c r="U79">
+        <v>0.26284999999999997</v>
+      </c>
+      <c r="V79">
+        <v>-0.16769999999999999</v>
+      </c>
+      <c r="W79">
+        <f t="shared" si="1"/>
+        <v>5.2824805021875605</v>
+      </c>
+    </row>
+    <row r="80" spans="19:23" x14ac:dyDescent="0.3">
+      <c r="S80">
+        <v>24.5</v>
+      </c>
+      <c r="T80">
+        <v>1.3872</v>
+      </c>
+      <c r="U80">
+        <v>0.27396999999999999</v>
+      </c>
+      <c r="V80">
+        <v>-0.17630000000000001</v>
+      </c>
+      <c r="W80">
+        <f t="shared" si="1"/>
+        <v>5.0633281016169658</v>
+      </c>
+    </row>
+    <row r="81" spans="19:23" x14ac:dyDescent="0.3">
+      <c r="S81">
+        <v>25</v>
+      </c>
+      <c r="T81">
+        <v>1.3883000000000001</v>
+      </c>
+      <c r="U81">
+        <v>0.28447</v>
+      </c>
+      <c r="V81">
+        <v>-0.18459999999999999</v>
+      </c>
+      <c r="W81">
+        <f t="shared" si="1"/>
+        <v>4.8803037227124131</v>
       </c>
     </row>
   </sheetData>
